--- a/data/CReDEs/v4/dg_ssjl.xlsx
+++ b/data/CReDEs/v4/dg_ssjl.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\东肝\CReDEs\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C185BE-B083-4C2E-BA39-754A48C1E0F6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF86B76-AAB8-4FC4-8887-114349A59C1F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{C9D0EE8C-C941-4C44-BF18-9CA2F4D57C75}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="179021" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/data/CReDEs/v4/dg_ssjl.xlsx
+++ b/data/CReDEs/v4/dg_ssjl.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\东肝\CReDEs\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF86B76-AAB8-4FC4-8887-114349A59C1F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6513B6-738A-4BEA-9646-2282FB8268E6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{C9D0EE8C-C941-4C44-BF18-9CA2F4D57C75}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021" concurrentCalc="0"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="150">
   <si>
     <t>标签类型</t>
   </si>
@@ -531,6 +531,10 @@
   </si>
   <si>
     <t>请填写以下选项：无，有，未描述,请填写以下选项：无，有，未描述,请填写以下选项：无，有，未描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写以下选项：无，轻，中，重，未查，未描述</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1746,7 +1750,7 @@
         <v>26</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="H35" s="3"/>
     </row>
@@ -1768,7 +1772,7 @@
         <v>26</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="H36" s="3"/>
     </row>
@@ -1790,7 +1794,7 @@
         <v>26</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="H37" s="3"/>
     </row>
